--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_antofagasta.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_antofagasta.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.0799582115766</v>
+      </c>
+      <c r="C2">
         <v>21.88063046012688</v>
-      </c>
-      <c r="C2">
-        <v>27.0799582115766</v>
       </c>
       <c r="D2">
         <v>4.570252222952635</v>
       </c>
       <c r="E2">
-        <v>14.68887217433729</v>
+        <v>18.17927711823061</v>
       </c>
       <c r="F2">
         <v>67.13185070743211</v>
       </c>
       <c r="G2">
-        <v>18.17927711823061</v>
+        <v>14.68887217433729</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>31.33404482390608</v>
+      </c>
+      <c r="C3">
         <v>19.32764140875133</v>
-      </c>
-      <c r="C3">
-        <v>31.33404482390608</v>
       </c>
       <c r="D3">
         <v>5.173937051352843</v>
       </c>
       <c r="E3">
-        <v>12.82850463979599</v>
+        <v>20.79761989091167</v>
       </c>
       <c r="F3">
         <v>66.37387546929234</v>
       </c>
       <c r="G3">
-        <v>20.79761989091167</v>
+        <v>12.82850463979599</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>36.11393692777213</v>
+      </c>
+      <c r="C4">
         <v>13.3265513733469</v>
-      </c>
-      <c r="C4">
-        <v>36.11393692777213</v>
       </c>
       <c r="D4">
         <v>7.503816793893129</v>
       </c>
       <c r="E4">
+        <v>24.16609938733833</v>
+      </c>
+      <c r="F4">
+        <v>66.91626957113684</v>
+      </c>
+      <c r="G4">
         <v>8.917631041524848</v>
-      </c>
-      <c r="F4">
-        <v>66.91626957113682</v>
-      </c>
-      <c r="G4">
-        <v>24.16609938733832</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>30.90223608944358</v>
+      </c>
+      <c r="C5">
         <v>30.03120124804992</v>
-      </c>
-      <c r="C5">
-        <v>30.90223608944358</v>
       </c>
       <c r="D5">
         <v>3.32987012987013</v>
       </c>
       <c r="E5">
-        <v>18.66063494627999</v>
+        <v>19.20187414169158</v>
       </c>
       <c r="F5">
         <v>62.13749091202843</v>
       </c>
       <c r="G5">
-        <v>19.20187414169158</v>
+        <v>18.66063494627999</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.30982215036379</v>
+      </c>
+      <c r="C6">
         <v>19.34283212072218</v>
-      </c>
-      <c r="C6">
-        <v>29.30982215036379</v>
       </c>
       <c r="D6">
         <v>5.169873748367436</v>
       </c>
       <c r="E6">
-        <v>13.01210006344603</v>
+        <v>19.71698540741412</v>
       </c>
       <c r="F6">
         <v>67.27091452913986</v>
       </c>
       <c r="G6">
-        <v>19.71698540741412</v>
+        <v>13.01210006344603</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>28.88888888888889</v>
+      </c>
+      <c r="C7">
         <v>16.2962962962963</v>
-      </c>
-      <c r="C7">
-        <v>28.88888888888889</v>
       </c>
       <c r="D7">
         <v>6.136363636363637</v>
       </c>
       <c r="E7">
-        <v>11.22448979591837</v>
+        <v>19.89795918367347</v>
       </c>
       <c r="F7">
         <v>68.87755102040816</v>
       </c>
       <c r="G7">
-        <v>19.89795918367347</v>
+        <v>11.22448979591837</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>29.43278943278943</v>
+      </c>
+      <c r="C8">
         <v>16.11499611499612</v>
-      </c>
-      <c r="C8">
-        <v>29.43278943278943</v>
       </c>
       <c r="D8">
         <v>6.205400192864031</v>
       </c>
       <c r="E8">
+        <v>20.22207986333547</v>
+      </c>
+      <c r="F8">
+        <v>68.70595771941062</v>
+      </c>
+      <c r="G8">
         <v>11.0719624172539</v>
-      </c>
-      <c r="F8">
-        <v>68.70595771941063</v>
-      </c>
-      <c r="G8">
-        <v>20.22207986333547</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>31.65652637521169</v>
+      </c>
+      <c r="C9">
         <v>30.52750423383303</v>
-      </c>
-      <c r="C9">
-        <v>31.65652637521169</v>
       </c>
       <c r="D9">
         <v>3.275734538730224</v>
       </c>
       <c r="E9">
-        <v>18.82275592682833</v>
+        <v>19.5188923695711</v>
       </c>
       <c r="F9">
         <v>61.65835170360057</v>
       </c>
       <c r="G9">
-        <v>19.5188923695711</v>
+        <v>18.82275592682833</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.54077253218884</v>
+      </c>
+      <c r="C10">
         <v>22.07234825260576</v>
-      </c>
-      <c r="C10">
-        <v>28.54077253218884</v>
       </c>
       <c r="D10">
         <v>4.530555555555556</v>
       </c>
       <c r="E10">
-        <v>14.65499694687563</v>
+        <v>18.94972521880725</v>
       </c>
       <c r="F10">
         <v>66.39527783431711</v>
       </c>
       <c r="G10">
-        <v>18.94972521880725</v>
+        <v>14.65499694687563</v>
       </c>
     </row>
   </sheetData>
